--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 DEER BUCK MANAGEMENT BUCK DEER ARCHERY.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 DEER BUCK MANAGEMENT BUCK DEER ARCHERY.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -569,10 +569,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -646,10 +651,11 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
